--- a/www/download/IND.surplus_value.empe.r.pc.rpA1.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.46</t>
+          <t>0.664598323040639</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>0.616531173146978</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66.88</t>
+          <t>0.668816206654015</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.66354986337525</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>0.577531064724958</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>0.650767597058911</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>0.695524127058846</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.11</t>
+          <t>0.621102900795054</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>0.523784033850346</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>0.325997992013917</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>0.260997225301435</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>0.293910344349957</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>0.272572615779619</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>0.405040393525742</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>0.464603367042592</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0332748396713736</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>0.072095119054733</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>0.263803121820995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>0.245866581226965</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>0.231646669472982</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>0.293069845652968</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>0.278152329583975</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0.270030819241277</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>0.170514915575773</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>0.124551501737705</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>0.109644445014416</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952214276963288</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>0.102373930931207</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>0.148708019099812</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.228954762810008</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-20.64</t>
+          <t>-0.206428111401855</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-0.22307174326833</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-18.6</t>
+          <t>-0.185951971788629</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-18.11</t>
+          <t>-0.181106222898996</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-25.14</t>
+          <t>-0.251385593664471</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-26.64</t>
+          <t>-0.266420980498826</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-0.307354117659617</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-36.1</t>
+          <t>-0.361007702254665</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-47.64</t>
+          <t>-0.476407140701992</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.1</t>
+          <t>-0.50104275971705</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-49.11</t>
+          <t>-0.491092186699805</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-48.27</t>
+          <t>-0.482730387561911</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-45.31</t>
+          <t>-0.45313271172534</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-39.2</t>
+          <t>-0.391963173716404</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-42.46</t>
+          <t>-0.42461551658137</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>261.67</t>
+          <t>2.61668010832426</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>305.57</t>
+          <t>3.05568846908364</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>359.87</t>
+          <t>3.59873811021994</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>268.19</t>
+          <t>2.68192288004558</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>305.92</t>
+          <t>3.05922774682048</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>323.6</t>
+          <t>3.2359807203999</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>313.75</t>
+          <t>3.13752453605095</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>332.06</t>
+          <t>3.32063439977028</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>330.72</t>
+          <t>3.30721018926812</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>341.48</t>
+          <t>3.4148131114046</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>355.64</t>
+          <t>3.55638383015997</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>372.9</t>
+          <t>3.72903536137669</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>358.63</t>
+          <t>3.58629333533617</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>332.31</t>
+          <t>3.32310531163477</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>288.39</t>
+          <t>2.88385839818964</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>201.42</t>
+          <t>2.01419426245393</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>206.43</t>
+          <t>2.06432243624933</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>224.09</t>
+          <t>2.24094121508035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>2.2153669835858</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>254.48</t>
+          <t>2.54479478462697</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>267.11</t>
+          <t>2.67113019911289</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>282.75</t>
+          <t>2.82752993804741</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>297.8</t>
+          <t>2.97797338807815</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>306.38</t>
+          <t>3.06378365897581</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>301.87</t>
+          <t>3.0186563289822</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>282.22</t>
+          <t>2.82218216288999</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>278.67</t>
+          <t>2.78673281342916</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>276.13</t>
+          <t>2.76132492675664</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>263.44</t>
+          <t>2.63438665778701</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>262.23</t>
+          <t>2.62232243862284</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>81.86</t>
+          <t>0.818594259879297</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>0.898107866706328</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>101.79</t>
+          <t>1.017882367132</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>0.895153511819487</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>81.37</t>
+          <t>0.8137240404713</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0.672021262808991</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>0.57767228880074</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58.06</t>
+          <t>0.5806251524851</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>48.26</t>
+          <t>0.482589471041621</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>0.433629675394372</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>0.331204164416463</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>0.286197329185258</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>0.347807104431641</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>0.376176884243725</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>0.491430720551704</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-30.96</t>
+          <t>-0.309569022010713</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-27.66</t>
+          <t>-0.276584293190659</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-0.253899079578999</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-0.220054777786919</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-0.176177333817714</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-0.114996724733306</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-0.0325915895807212</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>0.0328374413015295</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.105256326935899</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>0.169151211767705</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>0.234490334959236</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>0.280821216936531</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>0.426475820158198</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>0.446570743402694</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>0.491917164105396</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>0.8736235088376</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>81.95</t>
+          <t>0.81948716359057</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>110.3</t>
+          <t>1.10297153601649</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>1.02884417077934</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>0.857361139438874</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>0.909507773792884</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>0.755992709139054</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>72.01</t>
+          <t>0.720073053014404</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>52.66</t>
+          <t>0.526645962243092</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>58.36</t>
+          <t>0.583595925480849</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>62.27</t>
+          <t>0.622695756597988</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>0.652209037621321</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>0.833391517348711</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>0.579580240161285</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>0.936543402117422</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>358.31</t>
+          <t>3.58314157447121</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>221.22</t>
+          <t>2.21217438793539</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>246.06</t>
+          <t>2.46064847574539</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>240.62</t>
+          <t>2.40616773600468</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>242.73</t>
+          <t>2.42727482075363</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>256.66</t>
+          <t>2.56656587787055</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>223.97</t>
+          <t>2.23974882837087</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>210.59</t>
+          <t>2.10586145231085</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>182.03</t>
+          <t>1.82033878336446</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>163.33</t>
+          <t>1.63331689847174</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>154.84</t>
+          <t>1.54839405568761</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>164.7</t>
+          <t>1.64700468600266</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>160.28</t>
+          <t>1.60279242825954</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>166.06</t>
+          <t>1.66057462402128</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>204.68</t>
+          <t>2.04683746014502</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>-0.100963184994077</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.0110674389314516</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>0.124426429657262</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0908553436417376</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.0632262016892704</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.015762849229644</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.039016995549743</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.0359478675272324</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-0.0992556487907841</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-0.110011382353918</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-0.0725738536680243</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-0.0731622268260476</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-8.66</t>
+          <t>-0.0865535314270121</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.0299267696647173</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.00662697609272245</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-0.143904168957659</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>-0.122844545645351</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>0.149689848638703</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0540205085711951</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>0.0463281242946896</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>0.0996147491019657</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>0.056929224566572</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.0171946772946663</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-0.115723378731062</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-0.119863623218249</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-0.116768849543843</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-0.118963587142215</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-0.110926395079405</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-0.0473572676115802</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.0608622131544385</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>0.556071212157178</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>0.629638180906723</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>93.23</t>
+          <t>0.932255185363244</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77.81</t>
+          <t>0.778072795088969</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>0.683959785739098</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>0.714014742684382</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>61.81</t>
+          <t>0.61812610228978</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>0.545962740594873</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>0.401808373657899</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349221331840986</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>0.330727732733671</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.30877496041727</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0.320030395038575</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>0.352298835550102</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>50.08</t>
+          <t>0.50080048054822</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>301.2</t>
+          <t>3.01196357371098</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>271.38</t>
+          <t>2.71378759879344</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>257.73</t>
+          <t>2.57728034132979</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>234.92</t>
+          <t>2.34922818325084</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>242.91</t>
+          <t>2.42905808408777</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>195.15</t>
+          <t>1.95153756626269</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>191.43</t>
+          <t>1.91427369181817</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>134.72</t>
+          <t>1.34719368886788</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>1.0050152759114</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>94.55</t>
+          <t>0.945504724421768</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>111.47</t>
+          <t>1.11467865558604</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>118.29</t>
+          <t>1.18292169878075</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>110.04</t>
+          <t>1.10039326401738</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>92.84</t>
+          <t>0.928389761609394</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>0.992914570215438</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>0.315914287250077</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>0.289844317702558</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.545466909601312</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>0.454039377918215</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>0.4434373964857</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>0.595352325801307</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>0.547925296246569</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>0.529299055951674</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>0.371572952534813</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.310273558010121</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>0.283668815470102</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>0.240330922796197</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245603826339693</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>0.277611918191521</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0.3516426281804</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>0.219627271742545</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>0.224774067816705</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.420177264983795</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>0.283536380589272</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>0.202086631253894</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>0.194775956117893</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>0.132565889026003</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>0.0778098549663755</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.0112239393171794</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-0.0295676945145293</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-0.03458057691584</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.0129424070723346</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.00755792823735879</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0476204248970873</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>0.129818215048745</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>55.48</t>
+          <t>0.554760718185345</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>0.538935736197155</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>0.654310082819818</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>0.520239011698932</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>0.435343337242043</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>0.37612070374269</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>0.311675222366786</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.268817001634627</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>0.183781461599159</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.119027671924363</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>0.123507691371483</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>0.117968238446852</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>0.149475937678254</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>0.296392704648231</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>0.406955399259611</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>147.03</t>
+          <t>1.4702994306531</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>135.82</t>
+          <t>1.35816862322791</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>142.27</t>
+          <t>1.42271831942455</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>147.48</t>
+          <t>1.47482676075342</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>132.99</t>
+          <t>1.32989538878272</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>1.21296951405267</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>133.09</t>
+          <t>1.33090678413009</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>104.15</t>
+          <t>1.04148303989121</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>100.21</t>
+          <t>1.00205856645477</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>100.23</t>
+          <t>1.00228884741245</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>105.86</t>
+          <t>1.05862338589456</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>1.03596296110896</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>93.01</t>
+          <t>0.930098068288702</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>91.05</t>
+          <t>0.910547011515887</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>0.873330810104155</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>161.33</t>
+          <t>1.61329402871533</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>173.36</t>
+          <t>1.73359105225797</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>193.49</t>
+          <t>1.93493431539142</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>199.45</t>
+          <t>1.99453276893875</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>191.62</t>
+          <t>1.91621599491401</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>188.25</t>
+          <t>1.88247767909315</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>201.94</t>
+          <t>2.01942276235219</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>179.44</t>
+          <t>1.79442484749452</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>159.28</t>
+          <t>1.59276503103501</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>199.62</t>
+          <t>1.99617405434094</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>204.28</t>
+          <t>2.04277039468666</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>221.2</t>
+          <t>2.21204643642533</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>210.16</t>
+          <t>2.10157627802617</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>236.3</t>
+          <t>2.36297943060575</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>263.97</t>
+          <t>2.63968340937093</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>1.02103807950437</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>1.09196128202433</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>142.47</t>
+          <t>1.42469224042939</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>1.53442807762236</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>161.38</t>
+          <t>1.61378257620854</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>138.83</t>
+          <t>1.38827263055928</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>138.44</t>
+          <t>1.38444497873505</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>135.22</t>
+          <t>1.35224731319554</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>1.13375598209048</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>1.21120587794553</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>103.15</t>
+          <t>1.03152449129189</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>0.939227210426181</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>0.812701115547288</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>0.862886045005517</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>0.796023460493619</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>0.409106527489034</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.21</t>
+          <t>0.552115321613637</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48.97</t>
+          <t>0.489698832792453</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>0.51851919660964</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>0.553090566061692</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>0.589554959174993</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>57.51</t>
+          <t>0.575061999504409</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>0.610527749832624</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>0.539765759547074</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>48.14</t>
+          <t>0.481410728542208</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>0.435925712275245</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.40187147033257</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>0.436429058215255</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>0.492435552981991</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>0.433573813475373</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>0.562114069895103</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>0.539847312899525</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.66</t>
+          <t>0.766613903673606</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>0.856622812066091</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>0.872363305201601</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>85.45</t>
+          <t>0.854490560484014</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67.55</t>
+          <t>0.675549019086551</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>0.573608070373878</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>0.739195858194851</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>83.55</t>
+          <t>0.835532872826592</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>0.650694130817554</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>0.666286839825248</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528435380684596</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458155718374155</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>0.318911576580948</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>0.500372676581862</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>0.535375987497181</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>0.668967487426529</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>0.669005693921725</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>0.649294839139304</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>0.659578706671472</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>58.32</t>
+          <t>0.583249381949945</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>0.536857390867853</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>0.393440966549236</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>0.309849237343741</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>0.304371903766532</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>0.290926606249731</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>35.55</t>
+          <t>0.355497917886645</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>0.443249399158675</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>0.58839174983546</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>0.24376536601677</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>0.413876652691187</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.95</t>
+          <t>0.569481592300276</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.98</t>
+          <t>0.619765658326214</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>0.516024004631979</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435359951705457</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>0.452892979586315</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>0.515335977032704</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0.478222192030614</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.397631911394933</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>0.386136084398938</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.461549395517669</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>0.615756782310942</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>66.01</t>
+          <t>0.660082070229153</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>0.591271039835877</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>0.642695946653796</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>0.672102028726677</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>0.833031534836519</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>1.02675686604677</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>108.99</t>
+          <t>1.08987563790913</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>100.32</t>
+          <t>1.00323201325289</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>99.45</t>
+          <t>0.994505936813173</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>0.96120805710772</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>83.69</t>
+          <t>0.836905548736755</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>84.05</t>
+          <t>0.840485649555912</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>0.793961796019516</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>73.93</t>
+          <t>0.739252699311967</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>77.57</t>
+          <t>0.775726725810393</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>93.95</t>
+          <t>0.93949557787083</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>1.04621207069465</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>238.67</t>
+          <t>2.3867024426164</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>218.93</t>
+          <t>2.18932393599504</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>222.33</t>
+          <t>2.22334841135236</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>173.92</t>
+          <t>1.73916986407501</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>160.38</t>
+          <t>1.60380446728777</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>162.58</t>
+          <t>1.62576202284319</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>163.37</t>
+          <t>1.6337301282449</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>1.55204472709797</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>131.28</t>
+          <t>1.31276850943729</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>169.55</t>
+          <t>1.6955485374767</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>165.14</t>
+          <t>1.65137542510451</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>157.75</t>
+          <t>1.5775416731364</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>169.17</t>
+          <t>1.69165195948968</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>153.97</t>
+          <t>1.53971443175295</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>160.63</t>
+          <t>1.60632497111339</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>0.0708750202694166</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>0.23758374541677</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>0.472342744144288</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>0.492692052324917</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>0.425098197397545</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>0.404940315825611</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>0.536474482973778</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>0.439362922495499</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>0.373224436226269</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>0.333056082694016</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>0.279421598531489</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>0.324429827933629</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>0.509426604459347</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347349457136551</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>0.578436623139798</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>268.11</t>
+          <t>2.68110680270857</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>243.44</t>
+          <t>2.43444426846419</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>2.51501199566369</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>246.88</t>
+          <t>2.46884146937138</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>2.45001026964411</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>297.09</t>
+          <t>2.97088043697575</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>304.09</t>
+          <t>3.04087427967792</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>316.55</t>
+          <t>3.16549612578414</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>296.77</t>
+          <t>2.96774077542168</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>297.85</t>
+          <t>2.97848361935179</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>279.67</t>
+          <t>2.79665586014124</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>254.17</t>
+          <t>2.5416774829068</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>209.86</t>
+          <t>2.09857945516303</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>174.35</t>
+          <t>1.74354582738825</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>207.99</t>
+          <t>2.07986089993718</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>312.82</t>
+          <t>3.12818438531078</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>337.12</t>
+          <t>3.37122008347843</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>365.89</t>
+          <t>3.65889016329942</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>332.7</t>
+          <t>3.3270094424333</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>310.39</t>
+          <t>3.1038936631933</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>300.23</t>
+          <t>3.00231240748689</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>259.49</t>
+          <t>2.59494062487197</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>262.55</t>
+          <t>2.6255338097864</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>267.92</t>
+          <t>2.67922897500876</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>284.58</t>
+          <t>2.84582770857108</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>295.81</t>
+          <t>2.95812174159558</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>317.29</t>
+          <t>3.17288890607021</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>332.27</t>
+          <t>3.3227438746937</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>344.07</t>
+          <t>3.44071340490883</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>345.29</t>
+          <t>3.45291854206372</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>142.15</t>
+          <t>1.42148838035159</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>127.08</t>
+          <t>1.27078503844671</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>179.52</t>
+          <t>1.79516938086895</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>159.16</t>
+          <t>1.59163398580673</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>130.97</t>
+          <t>1.3097173183827</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>118.57</t>
+          <t>1.18569647671058</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>0.653983668217238</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>83.11</t>
+          <t>0.831101858782318</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>0.585448359453755</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>1.06898137829656</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>105.99</t>
+          <t>1.05986027296831</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>111.87</t>
+          <t>1.11874171824328</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>102.11</t>
+          <t>1.02111276809727</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>85.91</t>
+          <t>0.85906183218729</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>108.93</t>
+          <t>1.08928095174913</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-0.290041136764283</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-25.22</t>
+          <t>-0.252232622106706</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>0.0884066990054597</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-0.102568178240863</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>-0.149856680859093</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-9.8</t>
+          <t>-0.097996399624854</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-18.31</t>
+          <t>-0.183139769615625</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-0.269474724500033</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-26.16</t>
+          <t>-0.261605184911511</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-25.35</t>
+          <t>-0.253488935248356</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-23.1</t>
+          <t>-0.231028680839363</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-23.2</t>
+          <t>-0.231977270196437</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-0.225943992911716</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-25.79</t>
+          <t>-0.257868820725738</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-23.02</t>
+          <t>-0.230237313507472</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>80.84</t>
+          <t>0.808406420713102</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>0.716809161025854</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>0.702323129049663</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.27</t>
+          <t>0.652715882326953</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>78.41</t>
+          <t>0.78409374028383</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>0.898642409114783</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>141.33</t>
+          <t>1.41325409540367</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>148.86</t>
+          <t>1.48858960658987</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>159.07</t>
+          <t>1.59073854424555</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>175.3</t>
+          <t>1.75296304368269</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>164.59</t>
+          <t>1.64587314986701</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>172.98</t>
+          <t>1.72982833533483</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>175.72</t>
+          <t>1.75717047948662</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>163.84</t>
+          <t>1.63844368733231</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>190.22</t>
+          <t>1.90215541782303</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>96.41</t>
+          <t>0.964105241843298</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>0.929098229695221</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>124.47</t>
+          <t>1.24473340218029</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>105.53</t>
+          <t>1.05530459299143</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>109.02</t>
+          <t>1.0901944270322</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>105.4</t>
+          <t>1.05402730413646</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>97.45</t>
+          <t>0.974470613564698</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>1.00273021026805</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>0.941578397040298</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>96.19</t>
+          <t>0.961948030658886</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>0.989670153789383</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>119.47</t>
+          <t>1.19470941512424</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>120.51</t>
+          <t>1.20509518276777</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>113.41</t>
+          <t>1.13405000146074</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>150.67</t>
+          <t>1.50668645344002</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>144.26</t>
+          <t>1.44261211930666</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>1.50699691651178</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>179.74</t>
+          <t>1.7974496058231</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>123.14</t>
+          <t>1.23138712762604</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>122.47</t>
+          <t>1.22474054188314</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>0.909030959484068</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>78.42</t>
+          <t>0.784217540658486</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>137.96</t>
+          <t>1.37962851610738</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>131.72</t>
+          <t>1.31719722604625</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>180.19</t>
+          <t>1.80194414186875</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>144.68</t>
+          <t>1.44675064293867</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>158.83</t>
+          <t>1.5882666072718</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>145.02</t>
+          <t>1.45017768657067</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>128.15</t>
+          <t>1.28152784761111</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>155.22</t>
+          <t>1.55220864283066</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>111.95</t>
+          <t>1.11946189828245</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>1.01501702175449</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>119.97</t>
+          <t>1.19968360966772</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>132.82</t>
+          <t>1.32816401372185</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>149.91</t>
+          <t>1.49913472656511</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>1.23900212730366</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>129.14</t>
+          <t>1.29143514228465</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>121.26</t>
+          <t>1.21255241842549</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>102.32</t>
+          <t>1.02318161328552</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>95.09</t>
+          <t>0.950905805712151</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>0.88668657602627</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>0.904137609853271</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>0.727538630856746</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>0.505943020026413</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>0.490628279541511</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>415.09</t>
+          <t>4.15087239301128</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>379.86</t>
+          <t>3.79864979344385</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>396.45</t>
+          <t>3.96454956867561</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>390.53</t>
+          <t>3.90530066871525</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>419.42</t>
+          <t>4.19416130145137</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>404.85</t>
+          <t>4.04854851270759</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>391.68</t>
+          <t>3.91684567814297</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>381.05</t>
+          <t>3.81049664254242</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>313.26</t>
+          <t>3.13255632872121</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>240.3</t>
+          <t>2.40304864210153</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>243.31</t>
+          <t>2.43310441474169</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>222.38</t>
+          <t>2.22383145305368</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>174.88</t>
+          <t>1.74882266799196</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>184.29</t>
+          <t>1.8429402749934</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>133.61</t>
+          <t>1.336125182092</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>0.471446104923751</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>0.517683590466619</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>0.706733793805264</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.77</t>
+          <t>0.61772648930395</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>61.66</t>
+          <t>0.61663827517926</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>0.634604037784001</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>0.586471167526829</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>0.57564955133547</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>0.414986962187242</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>0.492565831842987</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>54.97</t>
+          <t>0.549739933374387</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>56.51</t>
+          <t>0.565076235763516</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>0.608525500787741</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>0.192256792407214</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213263340936556</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>0.289175690002637</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0.260037198895871</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>0.453483799303255</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>0.354740521279186</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>0.351913272360814</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>0.248028163993339</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.23902231654667</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>0.188766511168124</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0.0970716761484878</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0672207019422142</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>0.037055023105125</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>0.0444013332907129</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0195798833940541</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>0.146669072528613</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>0.307118032574667</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>179.63</t>
+          <t>1.79630562485449</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>152.99</t>
+          <t>1.52991596988046</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>144.04</t>
+          <t>1.44038617687122</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>140.63</t>
+          <t>1.40628849954202</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>122.87</t>
+          <t>1.22865429968475</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>159.84</t>
+          <t>1.59843678857622</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>179.12</t>
+          <t>1.79124408166103</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>217.99</t>
+          <t>2.17993323401579</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>205.61</t>
+          <t>2.05614335164169</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>187.87</t>
+          <t>1.87872071191131</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>2.08499966050859</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>223.07</t>
+          <t>2.23070856542834</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>218.52</t>
+          <t>2.18522635475124</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>0.879201880905864</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>1.08798824740332</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>0.656554443487451</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>0.547644569426972</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>0.742779137154988</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>0.813516650961366</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>0.850066338621485</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>75.81</t>
+          <t>0.758143907118317</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>0.6967563232137</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>0.737527801532134</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>74.04</t>
+          <t>0.740419015985979</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>0.77770485367161</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>0.801560164970953</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>86.83</t>
+          <t>0.868316209859665</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>1.09198331509608</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>1.10496161107426</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>132.31</t>
+          <t>1.3230673874809</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>0.749390870842535</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>0.784519934433816</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>0.781051005514336</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>0.691880635218429</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>0.644147013744164</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>0.489076493389305</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>0.428848450876868</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>0.387940808740614</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>0.339403285882754</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>0.313683667775286</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>0.309683845078383</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>0.344908184383151</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>0.447546818606871</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>53.99</t>
+          <t>0.539911664203745</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>56.79</t>
+          <t>0.567928264820756</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-0.078063805228755</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-0.0468195136731496</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-0.0584377963229399</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-0.0627809907874408</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-0.0840256097083344</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-0.103874246864209</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-0.0890467505576027</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-0.0761973034602529</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-0.0414285977068913</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.012780145356978</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.00276584253584344</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.00973193360849778</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>0.0782565715983214</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.10259951538686</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>0.127743747424557</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>0.140598240487321</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>0.187292511640481</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>0.208008344627336</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>0.213524912577429</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>0.221359190629187</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>0.217139038000674</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>0.234461278546946</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>0.2536637778758</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>0.25770816649188</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>0.283151708751415</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>0.28096292642969</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>0.291712789099648</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>0.362983436385461</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>38.92</t>
+          <t>0.389159333214274</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>0.410311726311331</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
